--- a/results/employee_performance_predictions.xlsx
+++ b/results/employee_performance_predictions.xlsx
@@ -4306,7 +4306,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -16906,7 +16906,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -18742,7 +18742,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -19030,7 +19030,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23242,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -23278,7 +23278,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues. Focus on faster bug identification and resolution.</t>
+          <t>Reduce system issues and improve reliability. Focus on faster bug identification and resolution.</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -27382,7 +27382,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -27886,7 +27886,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -27958,7 +27958,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -29722,7 +29722,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -33970,7 +33970,7 @@
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
         </is>
       </c>
       <c r="D939" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="E939" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
@@ -36454,7 +36454,7 @@
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>Improve system stability and reduce technical issues.</t>
+          <t>Reduce system issues and improve reliability.</t>
         </is>
       </c>
     </row>
